--- a/DataAnalysis/CJ/0.05/Results.xlsx
+++ b/DataAnalysis/CJ/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CJ\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA366078-78BA-41CD-927C-408B6D1711E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392AC44D-A9B3-4472-BB1E-1026B1D262E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -991,34 +991,34 @@
         <v>64</v>
       </c>
       <c r="G20">
-        <v>25.85</v>
+        <v>25.125</v>
       </c>
       <c r="H20">
-        <v>3.605936463358407</v>
+        <v>4.9560569003997523</v>
       </c>
       <c r="I20">
-        <v>13.2</v>
+        <v>10.875</v>
       </c>
       <c r="J20">
-        <v>2.1108186931983393</v>
+        <v>2.0966242709015206</v>
       </c>
       <c r="K20">
-        <v>34.700000000000003</v>
+        <v>35.75</v>
       </c>
       <c r="L20">
-        <v>3.301514803843836</v>
+        <v>2.9011491975882016</v>
       </c>
       <c r="M20">
-        <v>24.583333333333332</v>
+        <v>23.916666666666668</v>
       </c>
       <c r="N20">
-        <v>1.842988046155374</v>
+        <v>2.2709926039966328</v>
       </c>
       <c r="O20">
-        <v>11.383333333333333</v>
+        <v>13.041666666666668</v>
       </c>
       <c r="P20">
-        <v>1.6667592566873919</v>
+        <v>2.1142155536764347</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
@@ -4586,23 +4586,23 @@
         <v>52</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R34" si="0">AVERAGE(C3:D3)</f>
+        <f t="shared" ref="R3:R11" si="0">AVERAGE(C3:D3)</f>
         <v>27.5</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S34" si="1">AVERAGE(H3,I3)</f>
+        <f t="shared" ref="S3:S11" si="1">AVERAGE(H3,I3)</f>
         <v>14.5</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T34" si="2">AVERAGE(M3:N3)</f>
+        <f t="shared" ref="T3:T11" si="2">AVERAGE(M3:N3)</f>
         <v>38.5</v>
       </c>
       <c r="U3">
-        <f t="shared" ref="U3:U34" si="3">AVERAGE(R3:T3)</f>
+        <f t="shared" ref="U3:U11" si="3">AVERAGE(R3:T3)</f>
         <v>26.833333333333332</v>
       </c>
       <c r="AD3">
-        <f t="shared" ref="AD3:AD34" si="4">MIN(R3:T3)</f>
+        <f t="shared" ref="AD3:AD11" si="4">MIN(R3:T3)</f>
         <v>14.5</v>
       </c>
       <c r="AE3">
@@ -7076,7 +7076,7 @@
         <v>12.5</v>
       </c>
       <c r="V7">
-        <f t="shared" ref="V5:V15" si="10">(T7-U7)</f>
+        <f t="shared" ref="V7:V15" si="10">(T7-U7)</f>
         <v>13.833333333333332</v>
       </c>
       <c r="W7">
@@ -11930,19 +11930,19 @@
         <v>44</v>
       </c>
       <c r="Q16">
-        <f t="shared" ref="Q14:Q19" si="6">AVERAGE(C16:D16)</f>
+        <f t="shared" ref="Q16:Q19" si="6">AVERAGE(C16:D16)</f>
         <v>22.5</v>
       </c>
       <c r="R16">
-        <f t="shared" ref="R14:R19" si="7">AVERAGE(H16:I16)</f>
+        <f t="shared" ref="R16:R19" si="7">AVERAGE(H16:I16)</f>
         <v>11.5</v>
       </c>
       <c r="S16">
-        <f t="shared" ref="S14:S19" si="8">AVERAGE(M16:N16)</f>
+        <f t="shared" ref="S16:S19" si="8">AVERAGE(M16:N16)</f>
         <v>39</v>
       </c>
       <c r="T16">
-        <f t="shared" ref="T14:T19" si="9">AVERAGE(Q16:S16)</f>
+        <f t="shared" ref="T16:T19" si="9">AVERAGE(Q16:S16)</f>
         <v>24.333333333333332</v>
       </c>
       <c r="U16">
@@ -11978,11 +11978,11 @@
         <v>2.2709926039966328</v>
       </c>
       <c r="AC16">
-        <f t="shared" ref="AC14:AC19" si="10">MIN(Q16:S16)</f>
+        <f t="shared" ref="AC16:AC19" si="10">MIN(Q16:S16)</f>
         <v>11.5</v>
       </c>
       <c r="AD16">
-        <f t="shared" ref="AD14:AD19" si="11">T16-AC16</f>
+        <f t="shared" ref="AD16:AD19" si="11">T16-AC16</f>
         <v>12.833333333333332</v>
       </c>
       <c r="AE16">

--- a/DataAnalysis/CJ/0.05/Results.xlsx
+++ b/DataAnalysis/CJ/0.05/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CJ\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392AC44D-A9B3-4472-BB1E-1026B1D262E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6C171F-6229-4CBE-A0D3-CB5F4225735E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="71">
   <si>
     <t>Dati originali</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>ep=0.1</t>
+  </si>
+  <si>
+    <t>try3</t>
   </si>
 </sst>
 </file>
@@ -579,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -821,366 +824,401 @@
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12">
+        <v>27.3</v>
+      </c>
+      <c r="H12">
+        <v>0.90829510622924747</v>
+      </c>
+      <c r="I12">
+        <v>14.4</v>
+      </c>
+      <c r="J12">
+        <v>2.9240383034426913</v>
+      </c>
+      <c r="K12">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="L12">
+        <v>1.5247950681976905</v>
+      </c>
+      <c r="M12">
+        <v>26.466666666666669</v>
+      </c>
+      <c r="N12">
+        <v>0.96752835157999939</v>
+      </c>
+      <c r="O12">
+        <v>12.066666666666666</v>
+      </c>
+      <c r="P12">
+        <v>2.0702925182473915</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13">
-        <v>25.75</v>
-      </c>
-      <c r="H13">
-        <v>3.0299431604496405</v>
-      </c>
-      <c r="I13">
-        <v>13.6</v>
-      </c>
-      <c r="J13">
-        <v>1.663329993316623</v>
-      </c>
-      <c r="K13">
-        <v>38.1</v>
-      </c>
-      <c r="L13">
-        <v>2.9135697844549542</v>
-      </c>
-      <c r="M13">
-        <v>25.816666666666663</v>
-      </c>
-      <c r="N13">
-        <v>1.1849102690410829</v>
-      </c>
-      <c r="O13">
-        <v>12.216666666666669</v>
-      </c>
-      <c r="P13">
-        <v>1.0716607626126173</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14">
+        <v>25.75</v>
+      </c>
+      <c r="H14">
+        <v>3.0299431604496405</v>
+      </c>
+      <c r="I14">
+        <v>13.6</v>
+      </c>
+      <c r="J14">
+        <v>1.663329993316623</v>
+      </c>
+      <c r="K14">
+        <v>38.1</v>
+      </c>
+      <c r="L14">
+        <v>2.9135697844549542</v>
+      </c>
+      <c r="M14">
+        <v>25.816666666666663</v>
+      </c>
+      <c r="N14">
+        <v>1.1849102690410829</v>
+      </c>
+      <c r="O14">
+        <v>12.216666666666669</v>
+      </c>
+      <c r="P14">
+        <v>1.0716607626126173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C15" t="s">
         <v>2</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>22</v>
       </c>
-      <c r="G14">
+      <c r="G15">
         <v>24.5</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>2.4053511772118195</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>12.5625</v>
       </c>
-      <c r="J14">
+      <c r="J15">
         <v>1.9353386562267894</v>
       </c>
-      <c r="K14">
+      <c r="K15">
         <v>34.4375</v>
       </c>
-      <c r="L14">
+      <c r="L15">
         <v>2.9932960810069273</v>
       </c>
-      <c r="M14">
+      <c r="M15">
         <v>23.833333333333332</v>
       </c>
-      <c r="N14">
+      <c r="N15">
         <v>1.9189944456771324</v>
       </c>
-      <c r="O14">
+      <c r="O15">
         <v>11.270833333333332</v>
       </c>
-      <c r="P14">
+      <c r="P15">
         <v>1.3271807450979474</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17">
-        <v>23.714285714285715</v>
-      </c>
-      <c r="H17">
-        <v>2.6276913640612221</v>
-      </c>
-      <c r="I17">
-        <v>12.285714285714286</v>
-      </c>
-      <c r="J17">
-        <v>2.4127636791506446</v>
-      </c>
-      <c r="K17">
-        <v>37.214285714285715</v>
-      </c>
-      <c r="L17">
-        <v>3.4139071318303174</v>
-      </c>
-      <c r="M17">
-        <v>24.404761904761905</v>
-      </c>
-      <c r="N17">
-        <v>2.0634768009203559</v>
-      </c>
-      <c r="O17">
-        <v>12.11904761904762</v>
-      </c>
-      <c r="P17">
-        <v>1.8148418095390031</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>25.666666666666668</v>
+        <v>23.714285714285715</v>
       </c>
       <c r="H18">
-        <v>3.9958311609309392</v>
+        <v>2.6276913640612221</v>
       </c>
       <c r="I18">
-        <v>14.166666666666666</v>
+        <v>12.285714285714286</v>
       </c>
       <c r="J18">
-        <v>2.089657069154327</v>
+        <v>2.4127636791506446</v>
       </c>
       <c r="K18">
-        <v>36.833333333333336</v>
+        <v>37.214285714285715</v>
       </c>
       <c r="L18">
-        <v>1.5705625319186327</v>
+        <v>3.4139071318303174</v>
       </c>
       <c r="M18">
-        <v>25.555555555555554</v>
+        <v>24.404761904761905</v>
       </c>
       <c r="N18">
-        <v>1.4631270419005795</v>
+        <v>2.0634768009203559</v>
       </c>
       <c r="O18">
-        <v>11.388888888888891</v>
+        <v>12.11904761904762</v>
       </c>
       <c r="P18">
-        <v>1.8519259244444917</v>
+        <v>1.8148418095390031</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>25.666666666666668</v>
+      </c>
+      <c r="H19">
+        <v>3.9958311609309392</v>
+      </c>
+      <c r="I19">
+        <v>14.166666666666666</v>
+      </c>
+      <c r="J19">
+        <v>2.089657069154327</v>
+      </c>
+      <c r="K19">
+        <v>36.833333333333336</v>
+      </c>
+      <c r="L19">
+        <v>1.5705625319186327</v>
+      </c>
+      <c r="M19">
+        <v>25.555555555555554</v>
+      </c>
+      <c r="N19">
+        <v>1.4631270419005795</v>
+      </c>
+      <c r="O19">
+        <v>11.388888888888891</v>
+      </c>
+      <c r="P19">
+        <v>1.8519259244444917</v>
+      </c>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20">
-        <v>25.125</v>
-      </c>
-      <c r="H20">
-        <v>4.9560569003997523</v>
-      </c>
-      <c r="I20">
-        <v>10.875</v>
-      </c>
-      <c r="J20">
-        <v>2.0966242709015206</v>
-      </c>
-      <c r="K20">
-        <v>35.75</v>
-      </c>
-      <c r="L20">
-        <v>2.9011491975882016</v>
-      </c>
-      <c r="M20">
-        <v>23.916666666666668</v>
-      </c>
-      <c r="N20">
-        <v>2.2709926039966328</v>
-      </c>
-      <c r="O20">
-        <v>13.041666666666668</v>
-      </c>
-      <c r="P20">
-        <v>2.1142155536764347</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21">
+        <v>25.125</v>
+      </c>
+      <c r="H21">
+        <v>4.9560569003997523</v>
+      </c>
+      <c r="I21">
+        <v>10.875</v>
+      </c>
+      <c r="J21">
+        <v>2.0966242709015206</v>
+      </c>
+      <c r="K21">
+        <v>35.75</v>
+      </c>
+      <c r="L21">
+        <v>2.9011491975882016</v>
+      </c>
+      <c r="M21">
+        <v>23.916666666666668</v>
+      </c>
+      <c r="N21">
+        <v>2.2709926039966328</v>
+      </c>
+      <c r="O21">
+        <v>13.041666666666668</v>
+      </c>
+      <c r="P21">
+        <v>2.1142155536764347</v>
+      </c>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E22" t="s">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E23" t="s">
         <v>64</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>27.125</v>
       </c>
-      <c r="H22">
+      <c r="H23">
         <v>4.2695628191498329</v>
       </c>
-      <c r="I22">
+      <c r="I23">
         <v>13.5</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>2.1984843263788196</v>
       </c>
-      <c r="K22">
+      <c r="K23">
         <v>36.75</v>
       </c>
-      <c r="L22">
+      <c r="L23">
         <v>4.1932485418030412</v>
       </c>
-      <c r="M22">
+      <c r="M23">
         <v>25.791666666666668</v>
       </c>
-      <c r="N22">
+      <c r="N23">
         <v>2.0877730471237275</v>
       </c>
-      <c r="O22">
+      <c r="O23">
         <v>12.291666666666668</v>
       </c>
-      <c r="P22">
+      <c r="P23">
         <v>4.0377271751247248</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>24.75</v>
-      </c>
-      <c r="H25">
-        <v>1.7535677916750183</v>
-      </c>
-      <c r="I25">
-        <v>15.083333333333334</v>
-      </c>
-      <c r="J25">
-        <v>2.0103896803024659</v>
-      </c>
-      <c r="K25">
-        <v>36</v>
-      </c>
-      <c r="L25">
-        <v>2.9325756597230361</v>
-      </c>
-      <c r="M25">
-        <v>25.277777777777782</v>
-      </c>
-      <c r="N25">
-        <v>1.455513146116695</v>
-      </c>
-      <c r="O25">
-        <v>10.194444444444445</v>
-      </c>
-      <c r="P25">
-        <v>0.97420432870834284</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G26">
-        <v>21.5</v>
+        <v>24.75</v>
       </c>
       <c r="H26">
-        <v>2.6925824035672519</v>
+        <v>1.7535677916750183</v>
       </c>
       <c r="I26">
-        <v>13.7</v>
+        <v>15.083333333333334</v>
       </c>
       <c r="J26">
-        <v>0.83666002653407556</v>
+        <v>2.0103896803024659</v>
       </c>
       <c r="K26">
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="L26">
-        <v>4.5607017003965469</v>
+        <v>2.9325756597230361</v>
       </c>
       <c r="M26">
-        <v>23.533333333333335</v>
+        <v>25.277777777777782</v>
       </c>
       <c r="N26">
-        <v>2.4163792932585908</v>
+        <v>1.455513146116695</v>
       </c>
       <c r="O26">
-        <v>9.8333333333333339</v>
+        <v>10.194444444444445</v>
       </c>
       <c r="P26">
-        <v>2.0241596335818479</v>
+        <v>0.97420432870834284</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27">
+        <v>21.5</v>
+      </c>
+      <c r="H27">
+        <v>2.6925824035672519</v>
+      </c>
+      <c r="I27">
+        <v>13.7</v>
+      </c>
+      <c r="J27">
+        <v>0.83666002653407556</v>
+      </c>
+      <c r="K27">
+        <v>35.4</v>
+      </c>
+      <c r="L27">
+        <v>4.5607017003965469</v>
+      </c>
+      <c r="M27">
+        <v>23.533333333333335</v>
+      </c>
+      <c r="N27">
+        <v>2.4163792932585908</v>
+      </c>
+      <c r="O27">
+        <v>9.8333333333333339</v>
+      </c>
+      <c r="P27">
+        <v>2.0241596335818479</v>
+      </c>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D28" t="s">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D29" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E29" t="s">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
         <v>64</v>
       </c>
-      <c r="G29">
+      <c r="G30">
         <v>25</v>
       </c>
-      <c r="H29">
+      <c r="H30">
         <v>1.7795130420052185</v>
       </c>
-      <c r="I29">
+      <c r="I30">
         <v>13.625</v>
       </c>
-      <c r="J29">
+      <c r="J30">
         <v>1.5478479684172259</v>
       </c>
-      <c r="K29">
+      <c r="K30">
         <v>32.75</v>
       </c>
-      <c r="L29">
+      <c r="L30">
         <v>6.9821200218844703</v>
       </c>
-      <c r="M29">
+      <c r="M30">
         <v>23.791666666666664</v>
       </c>
-      <c r="N29">
+      <c r="N30">
         <v>2.5032386429790709</v>
       </c>
-      <c r="O29">
+      <c r="O30">
         <v>10.166666666666666</v>
       </c>
-      <c r="P29">
+      <c r="P30">
         <v>2.3174059571793588</v>
       </c>
     </row>
@@ -5113,7 +5151,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -5466,6 +5504,361 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>12.666666666666668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>74</v>
+      </c>
+      <c r="C9">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>28</v>
+      </c>
+      <c r="E9">
+        <v>72</v>
+      </c>
+      <c r="G9">
+        <v>82</v>
+      </c>
+      <c r="H9">
+        <v>18</v>
+      </c>
+      <c r="I9">
+        <v>9</v>
+      </c>
+      <c r="J9">
+        <v>91</v>
+      </c>
+      <c r="L9">
+        <v>66</v>
+      </c>
+      <c r="M9">
+        <v>34</v>
+      </c>
+      <c r="N9">
+        <v>39</v>
+      </c>
+      <c r="O9">
+        <v>61</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" ref="Q8:Q13" si="6">AVERAGE(C9:D9)</f>
+        <v>27</v>
+      </c>
+      <c r="R9">
+        <f t="shared" ref="R8:R13" si="7">AVERAGE(H9:I9)</f>
+        <v>13.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S8:S13" si="8">AVERAGE(M9:N9)</f>
+        <v>36.5</v>
+      </c>
+      <c r="T9">
+        <f t="shared" ref="T8:T13" si="9">AVERAGE(Q9:S9)</f>
+        <v>25.666666666666668</v>
+      </c>
+      <c r="U9">
+        <f>AVERAGE(Q9:Q13)</f>
+        <v>27.3</v>
+      </c>
+      <c r="V9">
+        <f>_xlfn.STDEV.S(Q9:Q13)</f>
+        <v>0.90829510622924747</v>
+      </c>
+      <c r="W9">
+        <f>AVERAGE(R9:R13)</f>
+        <v>14.4</v>
+      </c>
+      <c r="X9">
+        <f>_xlfn.STDEV.S(R9:R13)</f>
+        <v>2.9240383034426913</v>
+      </c>
+      <c r="Y9">
+        <f>AVERAGE(S9:S13)</f>
+        <v>37.700000000000003</v>
+      </c>
+      <c r="Z9">
+        <f>_xlfn.STDEV.S(S9:S13)</f>
+        <v>1.5247950681976905</v>
+      </c>
+      <c r="AA9">
+        <f>AVERAGE(T9:T13)</f>
+        <v>26.466666666666669</v>
+      </c>
+      <c r="AB9">
+        <f>_xlfn.STDEV.S(T9:T13)</f>
+        <v>0.96752835157999939</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" ref="AC8:AC13" si="10">MIN(Q9:S9)</f>
+        <v>13.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" ref="AD8:AD13" si="11">T9-AC9</f>
+        <v>12.166666666666668</v>
+      </c>
+      <c r="AE9">
+        <f>AVERAGE(AD9:AD13)</f>
+        <v>12.066666666666666</v>
+      </c>
+      <c r="AF9">
+        <f>_xlfn.STDEV.S(AD9:AD13)</f>
+        <v>2.0702925182473915</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>76</v>
+      </c>
+      <c r="C10">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>67</v>
+      </c>
+      <c r="G10">
+        <v>85</v>
+      </c>
+      <c r="H10">
+        <v>15</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>88</v>
+      </c>
+      <c r="L10">
+        <v>72</v>
+      </c>
+      <c r="M10">
+        <v>28</v>
+      </c>
+      <c r="N10">
+        <v>47</v>
+      </c>
+      <c r="O10">
+        <v>53</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="6"/>
+        <v>28.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="7"/>
+        <v>13.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="8"/>
+        <v>37.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="9"/>
+        <v>26.5</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="11"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>83</v>
+      </c>
+      <c r="C11">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>36</v>
+      </c>
+      <c r="E11">
+        <v>64</v>
+      </c>
+      <c r="G11">
+        <v>83</v>
+      </c>
+      <c r="H11">
+        <v>17</v>
+      </c>
+      <c r="I11">
+        <v>16</v>
+      </c>
+      <c r="J11">
+        <v>84</v>
+      </c>
+      <c r="L11">
+        <v>68</v>
+      </c>
+      <c r="M11">
+        <v>32</v>
+      </c>
+      <c r="N11">
+        <v>47</v>
+      </c>
+      <c r="O11">
+        <v>53</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>26.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>16.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>39.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>27.5</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>83</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>36</v>
+      </c>
+      <c r="E12">
+        <v>64</v>
+      </c>
+      <c r="G12">
+        <v>88</v>
+      </c>
+      <c r="H12">
+        <v>12</v>
+      </c>
+      <c r="I12">
+        <v>9</v>
+      </c>
+      <c r="J12">
+        <v>91</v>
+      </c>
+      <c r="L12">
+        <v>81</v>
+      </c>
+      <c r="M12">
+        <v>19</v>
+      </c>
+      <c r="N12">
+        <v>59</v>
+      </c>
+      <c r="O12">
+        <v>41</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>26.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>10.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>39</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>25.333333333333332</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>10.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>14.833333333333332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>88</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13">
+        <v>44</v>
+      </c>
+      <c r="E13">
+        <v>56</v>
+      </c>
+      <c r="G13">
+        <v>81</v>
+      </c>
+      <c r="H13">
+        <v>19</v>
+      </c>
+      <c r="I13">
+        <v>17</v>
+      </c>
+      <c r="J13">
+        <v>83</v>
+      </c>
+      <c r="L13">
+        <v>82</v>
+      </c>
+      <c r="M13">
+        <v>18</v>
+      </c>
+      <c r="N13">
+        <v>54</v>
+      </c>
+      <c r="O13">
+        <v>46</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>28</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>27.333333333333332</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>18</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>9.3333333333333321</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/CJ/0.05/Results.xlsx
+++ b/DataAnalysis/CJ/0.05/Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CJ\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6C171F-6229-4CBE-A0D3-CB5F4225735E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E166555-A3F5-428A-B91D-D44B151FD87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="72">
   <si>
     <t>Dati originali</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>try3</t>
+  </si>
+  <si>
+    <t>try:</t>
   </si>
 </sst>
 </file>
@@ -582,7 +585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -1060,166 +1063,309 @@
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D22" t="s">
+      <c r="F22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22">
+        <v>23.25</v>
+      </c>
+      <c r="H22">
+        <v>4.8733971724044816</v>
+      </c>
+      <c r="I22">
+        <v>11.125</v>
+      </c>
+      <c r="J22">
+        <v>1.75</v>
+      </c>
+      <c r="K22">
+        <v>35.375</v>
+      </c>
+      <c r="L22">
+        <v>2.6887109674836132</v>
+      </c>
+      <c r="M22">
+        <v>23.249999999999996</v>
+      </c>
+      <c r="N22">
+        <v>2.5549516194593154</v>
+      </c>
+      <c r="O22">
+        <v>12.125</v>
+      </c>
+      <c r="P22">
+        <v>1.7179606773406884</v>
+      </c>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E23" t="s">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
         <v>64</v>
       </c>
-      <c r="G23">
+      <c r="G24">
         <v>27.125</v>
       </c>
-      <c r="H23">
+      <c r="H24">
         <v>4.2695628191498329</v>
       </c>
-      <c r="I23">
+      <c r="I24">
         <v>13.5</v>
       </c>
-      <c r="J23">
+      <c r="J24">
         <v>2.1984843263788196</v>
       </c>
-      <c r="K23">
+      <c r="K24">
         <v>36.75</v>
       </c>
-      <c r="L23">
+      <c r="L24">
         <v>4.1932485418030412</v>
       </c>
-      <c r="M23">
+      <c r="M24">
         <v>25.791666666666668</v>
       </c>
-      <c r="N23">
+      <c r="N24">
         <v>2.0877730471237275</v>
       </c>
-      <c r="O23">
+      <c r="O24">
         <v>12.291666666666668</v>
       </c>
-      <c r="P23">
+      <c r="P24">
         <v>4.0377271751247248</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25">
+        <v>26.625</v>
+      </c>
+      <c r="H25">
+        <v>1.4361406616345072</v>
+      </c>
+      <c r="I25">
+        <v>12.25</v>
+      </c>
+      <c r="J25">
+        <v>1.8929694486000912</v>
+      </c>
+      <c r="K25">
+        <v>31.875</v>
+      </c>
+      <c r="L25">
+        <v>2.8686524130097508</v>
+      </c>
+      <c r="M25">
+        <v>23.583333333333336</v>
+      </c>
+      <c r="N25">
+        <v>1.158702978589679</v>
+      </c>
+      <c r="O25">
+        <v>11.333333333333336</v>
+      </c>
+      <c r="P25">
+        <v>2.3293616992485018</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
-        <v>4</v>
-      </c>
-      <c r="G26">
-        <v>24.75</v>
-      </c>
-      <c r="H26">
-        <v>1.7535677916750183</v>
-      </c>
-      <c r="I26">
-        <v>15.083333333333334</v>
-      </c>
-      <c r="J26">
-        <v>2.0103896803024659</v>
-      </c>
-      <c r="K26">
-        <v>36</v>
-      </c>
-      <c r="L26">
-        <v>2.9325756597230361</v>
-      </c>
-      <c r="M26">
-        <v>25.277777777777782</v>
-      </c>
-      <c r="N26">
-        <v>1.455513146116695</v>
-      </c>
-      <c r="O26">
-        <v>10.194444444444445</v>
-      </c>
-      <c r="P26">
-        <v>0.97420432870834284</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" t="s">
-        <v>22</v>
-      </c>
-      <c r="G27">
-        <v>21.5</v>
-      </c>
-      <c r="H27">
-        <v>2.6925824035672519</v>
-      </c>
-      <c r="I27">
-        <v>13.7</v>
-      </c>
-      <c r="J27">
-        <v>0.83666002653407556</v>
-      </c>
-      <c r="K27">
-        <v>35.4</v>
-      </c>
-      <c r="L27">
-        <v>4.5607017003965469</v>
-      </c>
-      <c r="M27">
-        <v>23.533333333333335</v>
-      </c>
-      <c r="N27">
-        <v>2.4163792932585908</v>
-      </c>
-      <c r="O27">
-        <v>9.8333333333333339</v>
-      </c>
-      <c r="P27">
-        <v>2.0241596335818479</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>24.75</v>
+      </c>
+      <c r="H28">
+        <v>1.7535677916750183</v>
+      </c>
+      <c r="I28">
+        <v>15.083333333333334</v>
+      </c>
+      <c r="J28">
+        <v>2.0103896803024659</v>
+      </c>
+      <c r="K28">
+        <v>36</v>
+      </c>
+      <c r="L28">
+        <v>2.9325756597230361</v>
+      </c>
+      <c r="M28">
+        <v>25.277777777777782</v>
+      </c>
+      <c r="N28">
+        <v>1.455513146116695</v>
+      </c>
+      <c r="O28">
+        <v>10.194444444444445</v>
+      </c>
+      <c r="P28">
+        <v>0.97420432870834284</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29">
+        <v>21.5</v>
+      </c>
+      <c r="H29">
+        <v>2.6925824035672519</v>
+      </c>
+      <c r="I29">
+        <v>13.7</v>
+      </c>
+      <c r="J29">
+        <v>0.83666002653407556</v>
+      </c>
+      <c r="K29">
+        <v>35.4</v>
+      </c>
+      <c r="L29">
+        <v>4.5607017003965469</v>
+      </c>
+      <c r="M29">
+        <v>23.533333333333335</v>
+      </c>
+      <c r="N29">
+        <v>2.4163792932585908</v>
+      </c>
+      <c r="O29">
+        <v>9.8333333333333339</v>
+      </c>
+      <c r="P29">
+        <v>2.0241596335818479</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D29" t="s">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D31" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31">
+        <v>23.25</v>
+      </c>
+      <c r="H31">
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="I31">
+        <v>12.5</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>30.5</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>22.083333333333336</v>
+      </c>
+      <c r="N31">
+        <v>0.8249579113843063</v>
+      </c>
+      <c r="O31">
+        <v>9.5833333333333339</v>
+      </c>
+      <c r="P31">
+        <v>0.8249579113843063</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E30" t="s">
+    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
         <v>64</v>
       </c>
-      <c r="G30">
+      <c r="G33">
         <v>25</v>
       </c>
-      <c r="H30">
+      <c r="H33">
         <v>1.7795130420052185</v>
       </c>
-      <c r="I30">
+      <c r="I33">
         <v>13.625</v>
       </c>
-      <c r="J30">
+      <c r="J33">
         <v>1.5478479684172259</v>
       </c>
-      <c r="K30">
+      <c r="K33">
         <v>32.75</v>
       </c>
-      <c r="L30">
+      <c r="L33">
         <v>6.9821200218844703</v>
       </c>
-      <c r="M30">
+      <c r="M33">
         <v>23.791666666666664</v>
       </c>
-      <c r="N30">
+      <c r="N33">
         <v>2.5032386429790709</v>
       </c>
-      <c r="O30">
+      <c r="O33">
         <v>10.166666666666666</v>
       </c>
-      <c r="P30">
+      <c r="P33">
         <v>2.3174059571793588</v>
+      </c>
+    </row>
+    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
+      <c r="E34" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34">
+        <v>25.25</v>
+      </c>
+      <c r="H34">
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="I34">
+        <v>13.5</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>33.75</v>
+      </c>
+      <c r="L34">
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="M34">
+        <v>24.166666666666664</v>
+      </c>
+      <c r="N34">
+        <v>0.47140452079103251</v>
+      </c>
+      <c r="O34">
+        <v>10.666666666666666</v>
+      </c>
+      <c r="P34">
+        <v>0.47140452079103251</v>
       </c>
     </row>
   </sheetData>
@@ -5549,19 +5695,19 @@
         <v>61</v>
       </c>
       <c r="Q9">
-        <f t="shared" ref="Q8:Q13" si="6">AVERAGE(C9:D9)</f>
+        <f t="shared" ref="Q9:Q13" si="6">AVERAGE(C9:D9)</f>
         <v>27</v>
       </c>
       <c r="R9">
-        <f t="shared" ref="R8:R13" si="7">AVERAGE(H9:I9)</f>
+        <f t="shared" ref="R9:R13" si="7">AVERAGE(H9:I9)</f>
         <v>13.5</v>
       </c>
       <c r="S9">
-        <f t="shared" ref="S8:S13" si="8">AVERAGE(M9:N9)</f>
+        <f t="shared" ref="S9:S13" si="8">AVERAGE(M9:N9)</f>
         <v>36.5</v>
       </c>
       <c r="T9">
-        <f t="shared" ref="T8:T13" si="9">AVERAGE(Q9:S9)</f>
+        <f t="shared" ref="T9:T13" si="9">AVERAGE(Q9:S9)</f>
         <v>25.666666666666668</v>
       </c>
       <c r="U9">
@@ -5597,11 +5743,11 @@
         <v>0.96752835157999939</v>
       </c>
       <c r="AC9">
-        <f t="shared" ref="AC8:AC13" si="10">MIN(Q9:S9)</f>
+        <f t="shared" ref="AC9:AC13" si="10">MIN(Q9:S9)</f>
         <v>13.5</v>
       </c>
       <c r="AD9">
-        <f t="shared" ref="AD8:AD13" si="11">T9-AC9</f>
+        <f t="shared" ref="AD9:AD13" si="11">T9-AC9</f>
         <v>12.166666666666668</v>
       </c>
       <c r="AE9">
@@ -10657,7 +10803,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11013,6 +11159,299 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>14.166666666666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>86</v>
+      </c>
+      <c r="C10">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>36</v>
+      </c>
+      <c r="E10">
+        <v>64</v>
+      </c>
+      <c r="G10">
+        <v>83</v>
+      </c>
+      <c r="H10">
+        <v>17</v>
+      </c>
+      <c r="I10">
+        <v>7</v>
+      </c>
+      <c r="J10">
+        <v>93</v>
+      </c>
+      <c r="L10">
+        <v>86</v>
+      </c>
+      <c r="M10">
+        <v>14</v>
+      </c>
+      <c r="N10">
+        <v>47</v>
+      </c>
+      <c r="O10">
+        <v>53</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ref="Q8:Q13" si="6">AVERAGE(C10:D10)</f>
+        <v>25</v>
+      </c>
+      <c r="R10">
+        <f t="shared" ref="R8:R13" si="7">AVERAGE(H10:I10)</f>
+        <v>12</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S8:S13" si="8">AVERAGE(M10:N10)</f>
+        <v>30.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T8:T13" si="9">AVERAGE(Q10:S10)</f>
+        <v>22.5</v>
+      </c>
+      <c r="U10">
+        <f>AVERAGE(Q10:Q13)</f>
+        <v>26.625</v>
+      </c>
+      <c r="V10">
+        <f>_xlfn.STDEV.S(Q10:Q13)</f>
+        <v>1.4361406616345072</v>
+      </c>
+      <c r="W10">
+        <f>AVERAGE(R10:R13)</f>
+        <v>12.25</v>
+      </c>
+      <c r="X10">
+        <f>_xlfn.STDEV.S(R10:R13)</f>
+        <v>1.8929694486000912</v>
+      </c>
+      <c r="Y10">
+        <f>AVERAGE(S10:S13)</f>
+        <v>31.875</v>
+      </c>
+      <c r="Z10">
+        <f>_xlfn.STDEV.S(S10:S13)</f>
+        <v>2.8686524130097508</v>
+      </c>
+      <c r="AA10">
+        <f>AVERAGE(T10:T13)</f>
+        <v>23.583333333333336</v>
+      </c>
+      <c r="AB10">
+        <f>_xlfn.STDEV.S(T10:T13)</f>
+        <v>1.158702978589679</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" ref="AC8:AC13" si="10">MIN(Q10:S10)</f>
+        <v>12</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" ref="AD8:AD13" si="11">T10-AC10</f>
+        <v>10.5</v>
+      </c>
+      <c r="AE10">
+        <f>AVERAGE(AD10:AD13)</f>
+        <v>11.333333333333336</v>
+      </c>
+      <c r="AF10">
+        <f>_xlfn.STDEV.S(AD10:AD13)</f>
+        <v>2.3293616992485018</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>85</v>
+      </c>
+      <c r="C11">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>38</v>
+      </c>
+      <c r="E11">
+        <v>62</v>
+      </c>
+      <c r="G11">
+        <v>91</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <v>13</v>
+      </c>
+      <c r="J11">
+        <v>87</v>
+      </c>
+      <c r="L11">
+        <v>86</v>
+      </c>
+      <c r="M11">
+        <v>14</v>
+      </c>
+      <c r="N11">
+        <v>49</v>
+      </c>
+      <c r="O11">
+        <v>51</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>26.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>31.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>23</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>83</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>89</v>
+      </c>
+      <c r="H12">
+        <v>11</v>
+      </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
+      <c r="J12">
+        <v>89</v>
+      </c>
+      <c r="L12">
+        <v>81</v>
+      </c>
+      <c r="M12">
+        <v>19</v>
+      </c>
+      <c r="N12">
+        <v>53</v>
+      </c>
+      <c r="O12">
+        <v>47</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>28.5</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>36</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>25.166666666666668</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>14.166666666666668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>82</v>
+      </c>
+      <c r="C13">
+        <v>18</v>
+      </c>
+      <c r="D13">
+        <v>35</v>
+      </c>
+      <c r="E13">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>79</v>
+      </c>
+      <c r="H13">
+        <v>21</v>
+      </c>
+      <c r="I13">
+        <v>9</v>
+      </c>
+      <c r="J13">
+        <v>91</v>
+      </c>
+      <c r="L13">
+        <v>73</v>
+      </c>
+      <c r="M13">
+        <v>27</v>
+      </c>
+      <c r="N13">
+        <v>32</v>
+      </c>
+      <c r="O13">
+        <v>68</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="6"/>
+        <v>26.5</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="8"/>
+        <v>29.5</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="9"/>
+        <v>23.666666666666668</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="10"/>
+        <v>15</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>8.6666666666666679</v>
       </c>
     </row>
   </sheetData>
@@ -11188,7 +11627,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
-  <dimension ref="A2:AF7"/>
+  <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -11544,6 +11983,175 @@
       <c r="AD7">
         <f t="shared" si="5"/>
         <v>11.333333333333332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>82</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>67</v>
+      </c>
+      <c r="G10">
+        <v>85</v>
+      </c>
+      <c r="H10">
+        <v>15</v>
+      </c>
+      <c r="I10">
+        <v>12</v>
+      </c>
+      <c r="J10">
+        <v>88</v>
+      </c>
+      <c r="L10">
+        <v>59</v>
+      </c>
+      <c r="M10">
+        <v>41</v>
+      </c>
+      <c r="N10">
+        <v>28</v>
+      </c>
+      <c r="O10">
+        <v>72</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" ref="Q8:Q11" si="6">AVERAGE(C10:D10)</f>
+        <v>25.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" ref="R8:R11" si="7">AVERAGE(H10:I10)</f>
+        <v>13.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S8:S11" si="8">AVERAGE(M10:N10)</f>
+        <v>34.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T8:T11" si="9">AVERAGE(Q10:S10)</f>
+        <v>24.5</v>
+      </c>
+      <c r="U10">
+        <f>AVERAGE(Q10:Q13)</f>
+        <v>25.25</v>
+      </c>
+      <c r="V10">
+        <f>_xlfn.STDEV.S(Q10:Q13)</f>
+        <v>0.35355339059327379</v>
+      </c>
+      <c r="W10">
+        <f>AVERAGE(R10:R13)</f>
+        <v>13.5</v>
+      </c>
+      <c r="X10">
+        <f>_xlfn.STDEV.S(R10:R13)</f>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f>AVERAGE(S10:S13)</f>
+        <v>33.75</v>
+      </c>
+      <c r="Z10">
+        <f>_xlfn.STDEV.S(S10:S12,S13)</f>
+        <v>1.0606601717798212</v>
+      </c>
+      <c r="AA10">
+        <f>AVERAGE(T10:T13)</f>
+        <v>24.166666666666664</v>
+      </c>
+      <c r="AB10">
+        <f>_xlfn.STDEV.S(T10:T13)</f>
+        <v>0.47140452079103251</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" ref="AC8:AC11" si="10">MIN(Q10:S10)</f>
+        <v>13.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" ref="AD8:AD11" si="11">T10-AC10</f>
+        <v>11</v>
+      </c>
+      <c r="AE10">
+        <f>AVERAGE(AD10:AD13)</f>
+        <v>10.666666666666666</v>
+      </c>
+      <c r="AF10">
+        <f>_xlfn.STDEV.S(AD10:AD13)</f>
+        <v>0.47140452079103251</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>91</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>41</v>
+      </c>
+      <c r="E11">
+        <v>59</v>
+      </c>
+      <c r="G11">
+        <v>91</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+      <c r="I11">
+        <v>18</v>
+      </c>
+      <c r="J11">
+        <v>82</v>
+      </c>
+      <c r="L11">
+        <v>86</v>
+      </c>
+      <c r="M11">
+        <v>14</v>
+      </c>
+      <c r="N11">
+        <v>52</v>
+      </c>
+      <c r="O11">
+        <v>48</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="7"/>
+        <v>13.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="8"/>
+        <v>33</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="9"/>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="10"/>
+        <v>13.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>10.333333333333332</v>
       </c>
     </row>
   </sheetData>
@@ -11553,7 +12161,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
-  <dimension ref="A2:AF19"/>
+  <dimension ref="A2:AF38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -12339,36 +12947,36 @@
         <v>24.333333333333332</v>
       </c>
       <c r="U16">
-        <f>AVERAGE(Q16:Q25)</f>
-        <v>25.125</v>
+        <f>AVERAGE(Q16:Q38)</f>
+        <v>24.1875</v>
       </c>
       <c r="V16">
-        <f>_xlfn.STDEV.S(Q16:Q25)</f>
-        <v>4.9560569003997523</v>
+        <f>_xlfn.STDEV.S(Q16:Q38)</f>
+        <v>4.659379940353805</v>
       </c>
       <c r="W16">
-        <f>AVERAGE(R16:R25)</f>
-        <v>10.875</v>
+        <f>AVERAGE(R16:R38)</f>
+        <v>11</v>
       </c>
       <c r="X16">
-        <f>_xlfn.STDEV.S(R16:R25)</f>
-        <v>2.0966242709015206</v>
+        <f>_xlfn.STDEV.S(R16:R38)</f>
+        <v>1.7928429140015905</v>
       </c>
       <c r="Y16">
-        <f>AVERAGE(S16:S25)</f>
-        <v>35.75</v>
+        <f>AVERAGE(S16:S38)</f>
+        <v>35.5625</v>
       </c>
       <c r="Z16">
-        <f>_xlfn.STDEV.S(S16:S25)</f>
-        <v>2.9011491975882016</v>
+        <f>_xlfn.STDEV.S(S16:S38)</f>
+        <v>2.5972169170644399</v>
       </c>
       <c r="AA16">
-        <f>AVERAGE(T16:T25)</f>
-        <v>23.916666666666668</v>
+        <f>AVERAGE(T16:T38)</f>
+        <v>23.583333333333336</v>
       </c>
       <c r="AB16">
-        <f>_xlfn.STDEV.S(T16:T25)</f>
-        <v>2.2709926039966328</v>
+        <f>_xlfn.STDEV.S(T16:T38)</f>
+        <v>2.2660363269199006</v>
       </c>
       <c r="AC16">
         <f t="shared" ref="AC16:AC19" si="10">MIN(Q16:S16)</f>
@@ -12379,12 +12987,12 @@
         <v>12.833333333333332</v>
       </c>
       <c r="AE16">
-        <f>AVERAGE(AD16:AD25)</f>
-        <v>13.041666666666668</v>
+        <f>AVERAGE(AD16:AD38)</f>
+        <v>12.583333333333332</v>
       </c>
       <c r="AF16">
-        <f>_xlfn.STDEV.S(AD16:AD25)</f>
-        <v>2.1142155536764347</v>
+        <f>_xlfn.STDEV.S(AD16:AD38)</f>
+        <v>1.8494958558036669</v>
       </c>
     </row>
     <row r="17" spans="2:30" x14ac:dyDescent="0.3">
@@ -12573,14 +13181,308 @@
         <v>13.166666666666668</v>
       </c>
     </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>84</v>
+      </c>
+      <c r="C35">
+        <v>16</v>
+      </c>
+      <c r="D35">
+        <v>42</v>
+      </c>
+      <c r="E35">
+        <v>58</v>
+      </c>
+      <c r="G35">
+        <v>91</v>
+      </c>
+      <c r="H35">
+        <v>9</v>
+      </c>
+      <c r="I35">
+        <v>15</v>
+      </c>
+      <c r="J35">
+        <v>85</v>
+      </c>
+      <c r="L35">
+        <v>91</v>
+      </c>
+      <c r="M35">
+        <v>9</v>
+      </c>
+      <c r="N35">
+        <v>67</v>
+      </c>
+      <c r="O35">
+        <v>33</v>
+      </c>
+      <c r="Q35">
+        <f>AVERAGE(C35:D35)</f>
+        <v>29</v>
+      </c>
+      <c r="R35">
+        <f>AVERAGE(H35:I35)</f>
+        <v>12</v>
+      </c>
+      <c r="S35">
+        <f>AVERAGE(M35:N35)</f>
+        <v>38</v>
+      </c>
+      <c r="T35">
+        <f>AVERAGE(Q35:S35)</f>
+        <v>26.333333333333332</v>
+      </c>
+      <c r="U35">
+        <f>AVERAGE(Q35:Q57)</f>
+        <v>23.25</v>
+      </c>
+      <c r="V35">
+        <f>_xlfn.STDEV.S(Q35:Q57)</f>
+        <v>4.8733971724044816</v>
+      </c>
+      <c r="W35">
+        <f>AVERAGE(R35:R57)</f>
+        <v>11.125</v>
+      </c>
+      <c r="X35">
+        <f>_xlfn.STDEV.S(R35:R57)</f>
+        <v>1.75</v>
+      </c>
+      <c r="Y35">
+        <f>AVERAGE(S35:S57)</f>
+        <v>35.375</v>
+      </c>
+      <c r="Z35">
+        <f>_xlfn.STDEV.S(S35:S57)</f>
+        <v>2.6887109674836132</v>
+      </c>
+      <c r="AA35">
+        <f>AVERAGE(T35:T57)</f>
+        <v>23.249999999999996</v>
+      </c>
+      <c r="AB35">
+        <f>_xlfn.STDEV.S(T35:T57)</f>
+        <v>2.5549516194593154</v>
+      </c>
+      <c r="AC35">
+        <f>MIN(Q35:S35)</f>
+        <v>12</v>
+      </c>
+      <c r="AD35">
+        <f>T35-AC35</f>
+        <v>14.333333333333332</v>
+      </c>
+      <c r="AE35">
+        <f>AVERAGE(AD35:AD57)</f>
+        <v>12.125</v>
+      </c>
+      <c r="AF35">
+        <f>_xlfn.STDEV.S(AD35:AD57)</f>
+        <v>1.7179606773406884</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>88</v>
+      </c>
+      <c r="C36">
+        <v>12</v>
+      </c>
+      <c r="D36">
+        <v>28</v>
+      </c>
+      <c r="E36">
+        <v>72</v>
+      </c>
+      <c r="G36">
+        <v>89</v>
+      </c>
+      <c r="H36">
+        <v>11</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36">
+        <v>90</v>
+      </c>
+      <c r="L36">
+        <v>82</v>
+      </c>
+      <c r="M36">
+        <v>18</v>
+      </c>
+      <c r="N36">
+        <v>46</v>
+      </c>
+      <c r="O36">
+        <v>54</v>
+      </c>
+      <c r="Q36">
+        <f>AVERAGE(C36:D36)</f>
+        <v>20</v>
+      </c>
+      <c r="R36">
+        <f>AVERAGE(H36:I36)</f>
+        <v>10.5</v>
+      </c>
+      <c r="S36">
+        <f>AVERAGE(M36:N36)</f>
+        <v>32</v>
+      </c>
+      <c r="T36">
+        <f>AVERAGE(Q36:S36)</f>
+        <v>20.833333333333332</v>
+      </c>
+      <c r="AC36">
+        <f>MIN(Q36:S36)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AD36">
+        <f>T36-AC36</f>
+        <v>10.333333333333332</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>90</v>
+      </c>
+      <c r="C37">
+        <v>10</v>
+      </c>
+      <c r="D37">
+        <v>27</v>
+      </c>
+      <c r="E37">
+        <v>73</v>
+      </c>
+      <c r="G37">
+        <v>89</v>
+      </c>
+      <c r="H37">
+        <v>11</v>
+      </c>
+      <c r="I37">
+        <v>7</v>
+      </c>
+      <c r="J37">
+        <v>93</v>
+      </c>
+      <c r="L37">
+        <v>82</v>
+      </c>
+      <c r="M37">
+        <v>18</v>
+      </c>
+      <c r="N37">
+        <v>56</v>
+      </c>
+      <c r="O37">
+        <v>44</v>
+      </c>
+      <c r="Q37">
+        <f>AVERAGE(C37:D37)</f>
+        <v>18.5</v>
+      </c>
+      <c r="R37">
+        <f>AVERAGE(H37:I37)</f>
+        <v>9</v>
+      </c>
+      <c r="S37">
+        <f>AVERAGE(M37:N37)</f>
+        <v>37</v>
+      </c>
+      <c r="T37">
+        <f>AVERAGE(Q37:S37)</f>
+        <v>21.5</v>
+      </c>
+      <c r="AC37">
+        <f>MIN(Q37:S37)</f>
+        <v>9</v>
+      </c>
+      <c r="AD37">
+        <f>T37-AC37</f>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>69</v>
+      </c>
+      <c r="C38">
+        <v>31</v>
+      </c>
+      <c r="D38">
+        <v>20</v>
+      </c>
+      <c r="E38">
+        <v>80</v>
+      </c>
+      <c r="G38">
+        <v>82</v>
+      </c>
+      <c r="H38">
+        <v>18</v>
+      </c>
+      <c r="I38">
+        <v>8</v>
+      </c>
+      <c r="J38">
+        <v>92</v>
+      </c>
+      <c r="L38">
+        <v>73</v>
+      </c>
+      <c r="M38">
+        <v>27</v>
+      </c>
+      <c r="N38">
+        <v>42</v>
+      </c>
+      <c r="O38">
+        <v>58</v>
+      </c>
+      <c r="Q38">
+        <f>AVERAGE(C38:D38)</f>
+        <v>25.5</v>
+      </c>
+      <c r="R38">
+        <f>AVERAGE(H38:I38)</f>
+        <v>13</v>
+      </c>
+      <c r="S38">
+        <f>AVERAGE(M38:N38)</f>
+        <v>34.5</v>
+      </c>
+      <c r="T38">
+        <f>AVERAGE(Q38:S38)</f>
+        <v>24.333333333333332</v>
+      </c>
+      <c r="AC38">
+        <f>MIN(Q38:S38)</f>
+        <v>13</v>
+      </c>
+      <c r="AD38">
+        <f>T38-AC38</f>
+        <v>11.333333333333332</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
-  <dimension ref="A2:AF8"/>
+  <dimension ref="A2:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
@@ -12995,6 +13897,175 @@
       <c r="AD8">
         <f t="shared" si="5"/>
         <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>87</v>
+      </c>
+      <c r="C11">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>70</v>
+      </c>
+      <c r="G11">
+        <v>94</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>19</v>
+      </c>
+      <c r="J11">
+        <v>81</v>
+      </c>
+      <c r="L11">
+        <v>74</v>
+      </c>
+      <c r="M11">
+        <v>26</v>
+      </c>
+      <c r="N11">
+        <v>35</v>
+      </c>
+      <c r="O11">
+        <v>65</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" ref="Q9:Q12" si="6">AVERAGE(C11:D11)</f>
+        <v>21.5</v>
+      </c>
+      <c r="R11">
+        <f t="shared" ref="R9:R12" si="7">AVERAGE(H11:I11)</f>
+        <v>12.5</v>
+      </c>
+      <c r="S11">
+        <f t="shared" ref="S9:S12" si="8">AVERAGE(M11:N11)</f>
+        <v>30.5</v>
+      </c>
+      <c r="T11">
+        <f t="shared" ref="T9:T12" si="9">AVERAGE(Q11:S11)</f>
+        <v>21.5</v>
+      </c>
+      <c r="U11">
+        <f>AVERAGE(Q11:Q15)</f>
+        <v>23.25</v>
+      </c>
+      <c r="V11">
+        <f>_xlfn.STDEV.S(Q11:Q15)</f>
+        <v>2.4748737341529163</v>
+      </c>
+      <c r="W11">
+        <f>AVERAGE(R11:R15)</f>
+        <v>12.5</v>
+      </c>
+      <c r="X11">
+        <f>_xlfn.STDEV.S(R11:R15)</f>
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <f>AVERAGE(S11:S15)</f>
+        <v>30.5</v>
+      </c>
+      <c r="Z11">
+        <f>_xlfn.STDEV.S(S11:S15)</f>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f>AVERAGE(T11:T15)</f>
+        <v>22.083333333333336</v>
+      </c>
+      <c r="AB11">
+        <f>_xlfn.STDEV.S(T11:T15)</f>
+        <v>0.8249579113843063</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" ref="AC9:AC12" si="10">MIN(Q11:S11)</f>
+        <v>12.5</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" ref="AD9:AD12" si="11">T11-AC11</f>
+        <v>9</v>
+      </c>
+      <c r="AE11">
+        <f>AVERAGE(AD11:AD15)</f>
+        <v>9.5833333333333339</v>
+      </c>
+      <c r="AF11">
+        <f>_xlfn.STDEV.S(AD11:AD15)</f>
+        <v>0.8249579113843063</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>83</v>
+      </c>
+      <c r="C12">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>67</v>
+      </c>
+      <c r="G12">
+        <v>92</v>
+      </c>
+      <c r="H12">
+        <v>8</v>
+      </c>
+      <c r="I12">
+        <v>17</v>
+      </c>
+      <c r="J12">
+        <v>83</v>
+      </c>
+      <c r="L12">
+        <v>75</v>
+      </c>
+      <c r="M12">
+        <v>25</v>
+      </c>
+      <c r="N12">
+        <v>36</v>
+      </c>
+      <c r="O12">
+        <v>64</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="7"/>
+        <v>12.5</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="8"/>
+        <v>30.5</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="9"/>
+        <v>22.666666666666668</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>10.166666666666668</v>
       </c>
     </row>
   </sheetData>

--- a/DataAnalysis/CJ/0.05/Results.xlsx
+++ b/DataAnalysis/CJ/0.05/Results.xlsx
@@ -8,28 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\CJ\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E166555-A3F5-428A-B91D-D44B151FD87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7E4867-5CEB-44D3-8BAD-7908E2B380CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
-    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId2"/>
-    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId3"/>
-    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId4"/>
-    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId5"/>
-    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId6"/>
-    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId7"/>
-    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId8"/>
-    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId9"/>
-    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId10"/>
-    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId11"/>
-    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId12"/>
-    <sheet name="DIFF" sheetId="8" r:id="rId13"/>
-    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId14"/>
-    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId15"/>
-    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId16"/>
-    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId17"/>
+    <sheet name="DIFF_ONLYMIN" sheetId="20" r:id="rId2"/>
+    <sheet name="MIT_DIFF_ONLYMIN_STDAUG" sheetId="19" r:id="rId3"/>
+    <sheet name="MIT_DIFF_ONLYMIN_NOAUG" sheetId="18" r:id="rId4"/>
+    <sheet name="MIT_PARBS_DIFF_ONLYMIN_STDAUG" sheetId="17" r:id="rId5"/>
+    <sheet name="MIT_DIFF_STDAUG" sheetId="16" r:id="rId6"/>
+    <sheet name="MIT_PARBS_STDAUG" sheetId="14" r:id="rId7"/>
+    <sheet name="MIT_DIFF_NOAUG" sheetId="15" r:id="rId8"/>
+    <sheet name="MIT_PARBS_NOAUG" sheetId="13" r:id="rId9"/>
+    <sheet name="MIT_NOAUG" sheetId="11" r:id="rId10"/>
+    <sheet name="MIT_STDAUG" sheetId="12" r:id="rId11"/>
+    <sheet name="STD_IMB_AUG" sheetId="10" r:id="rId12"/>
+    <sheet name="STD_IMB_NOAUG" sheetId="9" r:id="rId13"/>
+    <sheet name="DIFF" sheetId="8" r:id="rId14"/>
+    <sheet name="STD_BAL_ADV_NOCLSDIV" sheetId="7" r:id="rId15"/>
+    <sheet name="STD_BAL_ADV_CLSDIV" sheetId="6" r:id="rId16"/>
+    <sheet name="STD_BAL_STDAUG" sheetId="5" r:id="rId17"/>
+    <sheet name="STD_BAL_NOAUG" sheetId="2" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="72">
   <si>
     <t>Dati originali</t>
   </si>
@@ -585,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.88671875" customWidth="1"/>
@@ -862,509 +863,547 @@
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13">
+        <v>23</v>
+      </c>
+      <c r="H13">
+        <v>1.8708286933869707</v>
+      </c>
+      <c r="I13">
+        <v>13.5</v>
+      </c>
+      <c r="J13">
+        <v>2.4494897427831779</v>
+      </c>
+      <c r="K13">
+        <v>35.625</v>
+      </c>
+      <c r="L13">
+        <v>0.8539125638299665</v>
+      </c>
+      <c r="M13">
+        <v>24.041666666666668</v>
+      </c>
+      <c r="N13">
+        <v>1.1656741810198499</v>
+      </c>
+      <c r="O13">
+        <v>10.541666666666668</v>
+      </c>
+      <c r="P13">
+        <v>1.4231876063832671</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C14" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
         <v>4</v>
       </c>
-      <c r="G14">
+      <c r="G16">
         <v>25.75</v>
       </c>
-      <c r="H14">
+      <c r="H16">
         <v>3.0299431604496405</v>
       </c>
-      <c r="I14">
+      <c r="I16">
         <v>13.6</v>
       </c>
-      <c r="J14">
+      <c r="J16">
         <v>1.663329993316623</v>
       </c>
-      <c r="K14">
+      <c r="K16">
         <v>38.1</v>
       </c>
-      <c r="L14">
+      <c r="L16">
         <v>2.9135697844549542</v>
       </c>
-      <c r="M14">
+      <c r="M16">
         <v>25.816666666666663</v>
       </c>
-      <c r="N14">
+      <c r="N16">
         <v>1.1849102690410829</v>
       </c>
-      <c r="O14">
+      <c r="O16">
         <v>12.216666666666669</v>
       </c>
-      <c r="P14">
+      <c r="P16">
         <v>1.0716607626126173</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C15" t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>2</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F17" t="s">
         <v>22</v>
       </c>
-      <c r="G15">
+      <c r="G17">
         <v>24.5</v>
       </c>
-      <c r="H15">
+      <c r="H17">
         <v>2.4053511772118195</v>
       </c>
-      <c r="I15">
+      <c r="I17">
         <v>12.5625</v>
       </c>
-      <c r="J15">
+      <c r="J17">
         <v>1.9353386562267894</v>
       </c>
-      <c r="K15">
+      <c r="K17">
         <v>34.4375</v>
       </c>
-      <c r="L15">
+      <c r="L17">
         <v>2.9932960810069273</v>
       </c>
-      <c r="M15">
+      <c r="M17">
         <v>23.833333333333332</v>
       </c>
-      <c r="N15">
+      <c r="N17">
         <v>1.9189944456771324</v>
       </c>
-      <c r="O15">
+      <c r="O17">
         <v>11.270833333333332</v>
       </c>
-      <c r="P15">
+      <c r="P17">
         <v>1.3271807450979474</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>4</v>
       </c>
-      <c r="G18">
+      <c r="G20">
         <v>23.714285714285715</v>
       </c>
-      <c r="H18">
+      <c r="H20">
         <v>2.6276913640612221</v>
       </c>
-      <c r="I18">
+      <c r="I20">
         <v>12.285714285714286</v>
       </c>
-      <c r="J18">
+      <c r="J20">
         <v>2.4127636791506446</v>
       </c>
-      <c r="K18">
+      <c r="K20">
         <v>37.214285714285715</v>
       </c>
-      <c r="L18">
+      <c r="L20">
         <v>3.4139071318303174</v>
       </c>
-      <c r="M18">
+      <c r="M20">
         <v>24.404761904761905</v>
       </c>
-      <c r="N18">
+      <c r="N20">
         <v>2.0634768009203559</v>
       </c>
-      <c r="O18">
+      <c r="O20">
         <v>12.11904761904762</v>
       </c>
-      <c r="P18">
+      <c r="P20">
         <v>1.8148418095390031</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
         <v>64</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F21" t="s">
         <v>22</v>
       </c>
-      <c r="G19">
+      <c r="G21">
         <v>25.666666666666668</v>
       </c>
-      <c r="H19">
+      <c r="H21">
         <v>3.9958311609309392</v>
       </c>
-      <c r="I19">
+      <c r="I21">
         <v>14.166666666666666</v>
       </c>
-      <c r="J19">
+      <c r="J21">
         <v>2.089657069154327</v>
       </c>
-      <c r="K19">
+      <c r="K21">
         <v>36.833333333333336</v>
       </c>
-      <c r="L19">
+      <c r="L21">
         <v>1.5705625319186327</v>
       </c>
-      <c r="M19">
+      <c r="M21">
         <v>25.555555555555554</v>
       </c>
-      <c r="N19">
+      <c r="N21">
         <v>1.4631270419005795</v>
       </c>
-      <c r="O19">
+      <c r="O21">
         <v>11.388888888888891</v>
       </c>
-      <c r="P19">
+      <c r="P21">
         <v>1.8519259244444917</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D21" t="s">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
         <v>64</v>
       </c>
-      <c r="G21">
+      <c r="G23">
         <v>25.125</v>
       </c>
-      <c r="H21">
+      <c r="H23">
         <v>4.9560569003997523</v>
       </c>
-      <c r="I21">
+      <c r="I23">
         <v>10.875</v>
       </c>
-      <c r="J21">
+      <c r="J23">
         <v>2.0966242709015206</v>
       </c>
-      <c r="K21">
+      <c r="K23">
         <v>35.75</v>
       </c>
-      <c r="L21">
+      <c r="L23">
         <v>2.9011491975882016</v>
       </c>
-      <c r="M21">
+      <c r="M23">
         <v>23.916666666666668</v>
       </c>
-      <c r="N21">
+      <c r="N23">
         <v>2.2709926039966328</v>
       </c>
-      <c r="O21">
+      <c r="O23">
         <v>13.041666666666668</v>
       </c>
-      <c r="P21">
+      <c r="P23">
         <v>2.1142155536764347</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="F22" t="s">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
         <v>70</v>
       </c>
-      <c r="G22">
+      <c r="G24">
         <v>23.25</v>
       </c>
-      <c r="H22">
+      <c r="H24">
         <v>4.8733971724044816</v>
       </c>
-      <c r="I22">
+      <c r="I24">
         <v>11.125</v>
       </c>
-      <c r="J22">
+      <c r="J24">
         <v>1.75</v>
       </c>
-      <c r="K22">
+      <c r="K24">
         <v>35.375</v>
       </c>
-      <c r="L22">
+      <c r="L24">
         <v>2.6887109674836132</v>
       </c>
-      <c r="M22">
+      <c r="M24">
         <v>23.249999999999996</v>
       </c>
-      <c r="N22">
+      <c r="N24">
         <v>2.5549516194593154</v>
       </c>
-      <c r="O22">
+      <c r="O24">
         <v>12.125</v>
       </c>
-      <c r="P22">
+      <c r="P24">
         <v>1.7179606773406884</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D23" t="s">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="E24" t="s">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E26" t="s">
         <v>64</v>
       </c>
-      <c r="G24">
+      <c r="G26">
         <v>27.125</v>
       </c>
-      <c r="H24">
+      <c r="H26">
         <v>4.2695628191498329</v>
       </c>
-      <c r="I24">
+      <c r="I26">
         <v>13.5</v>
       </c>
-      <c r="J24">
+      <c r="J26">
         <v>2.1984843263788196</v>
       </c>
-      <c r="K24">
+      <c r="K26">
         <v>36.75</v>
       </c>
-      <c r="L24">
+      <c r="L26">
         <v>4.1932485418030412</v>
       </c>
-      <c r="M24">
+      <c r="M26">
         <v>25.791666666666668</v>
       </c>
-      <c r="N24">
+      <c r="N26">
         <v>2.0877730471237275</v>
       </c>
-      <c r="O24">
+      <c r="O26">
         <v>12.291666666666668</v>
       </c>
-      <c r="P24">
+      <c r="P26">
         <v>4.0377271751247248</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="F25" t="s">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
         <v>70</v>
       </c>
-      <c r="G25">
+      <c r="G27">
         <v>26.625</v>
       </c>
-      <c r="H25">
+      <c r="H27">
         <v>1.4361406616345072</v>
       </c>
-      <c r="I25">
+      <c r="I27">
         <v>12.25</v>
       </c>
-      <c r="J25">
+      <c r="J27">
         <v>1.8929694486000912</v>
       </c>
-      <c r="K25">
+      <c r="K27">
         <v>31.875</v>
       </c>
-      <c r="L25">
+      <c r="L27">
         <v>2.8686524130097508</v>
       </c>
-      <c r="M25">
+      <c r="M27">
         <v>23.583333333333336</v>
       </c>
-      <c r="N25">
+      <c r="N27">
         <v>1.158702978589679</v>
       </c>
-      <c r="O25">
+      <c r="O27">
         <v>11.333333333333336</v>
       </c>
-      <c r="P25">
+      <c r="P27">
         <v>2.3293616992485018</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>4</v>
       </c>
-      <c r="G28">
+      <c r="G30">
         <v>24.75</v>
       </c>
-      <c r="H28">
+      <c r="H30">
         <v>1.7535677916750183</v>
       </c>
-      <c r="I28">
+      <c r="I30">
         <v>15.083333333333334</v>
       </c>
-      <c r="J28">
+      <c r="J30">
         <v>2.0103896803024659</v>
       </c>
-      <c r="K28">
+      <c r="K30">
         <v>36</v>
       </c>
-      <c r="L28">
+      <c r="L30">
         <v>2.9325756597230361</v>
       </c>
-      <c r="M28">
+      <c r="M30">
         <v>25.277777777777782</v>
       </c>
-      <c r="N28">
+      <c r="N30">
         <v>1.455513146116695</v>
       </c>
-      <c r="O28">
+      <c r="O30">
         <v>10.194444444444445</v>
       </c>
-      <c r="P28">
+      <c r="P30">
         <v>0.97420432870834284</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
         <v>64</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F31" t="s">
         <v>22</v>
       </c>
-      <c r="G29">
+      <c r="G31">
         <v>21.5</v>
       </c>
-      <c r="H29">
+      <c r="H31">
         <v>2.6925824035672519</v>
       </c>
-      <c r="I29">
+      <c r="I31">
         <v>13.7</v>
       </c>
-      <c r="J29">
+      <c r="J31">
         <v>0.83666002653407556</v>
       </c>
-      <c r="K29">
+      <c r="K31">
         <v>35.4</v>
       </c>
-      <c r="L29">
+      <c r="L31">
         <v>4.5607017003965469</v>
       </c>
-      <c r="M29">
+      <c r="M31">
         <v>23.533333333333335</v>
       </c>
-      <c r="N29">
+      <c r="N31">
         <v>2.4163792932585908</v>
       </c>
-      <c r="O29">
+      <c r="O31">
         <v>9.8333333333333339</v>
       </c>
-      <c r="P29">
+      <c r="P31">
         <v>2.0241596335818479</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="C30" t="s">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D31" t="s">
+    <row r="33" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
         <v>2</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E33" t="s">
         <v>70</v>
       </c>
-      <c r="G31">
+      <c r="G33">
         <v>23.25</v>
       </c>
-      <c r="H31">
+      <c r="H33">
         <v>2.4748737341529163</v>
       </c>
-      <c r="I31">
+      <c r="I33">
         <v>12.5</v>
       </c>
-      <c r="J31">
+      <c r="J33">
         <v>0</v>
       </c>
-      <c r="K31">
+      <c r="K33">
         <v>30.5</v>
       </c>
-      <c r="L31">
+      <c r="L33">
         <v>0</v>
       </c>
-      <c r="M31">
+      <c r="M33">
         <v>22.083333333333336</v>
       </c>
-      <c r="N31">
+      <c r="N33">
         <v>0.8249579113843063</v>
       </c>
-      <c r="O31">
+      <c r="O33">
         <v>9.5833333333333339</v>
       </c>
-      <c r="P31">
+      <c r="P33">
         <v>0.8249579113843063</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D32" t="s">
+    <row r="34" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E33" t="s">
+    <row r="35" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
         <v>64</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <v>25</v>
       </c>
-      <c r="H33">
+      <c r="H35">
         <v>1.7795130420052185</v>
       </c>
-      <c r="I33">
+      <c r="I35">
         <v>13.625</v>
       </c>
-      <c r="J33">
+      <c r="J35">
         <v>1.5478479684172259</v>
       </c>
-      <c r="K33">
+      <c r="K35">
         <v>32.75</v>
       </c>
-      <c r="L33">
+      <c r="L35">
         <v>6.9821200218844703</v>
       </c>
-      <c r="M33">
+      <c r="M35">
         <v>23.791666666666664</v>
       </c>
-      <c r="N33">
+      <c r="N35">
         <v>2.5032386429790709</v>
       </c>
-      <c r="O33">
+      <c r="O35">
         <v>10.166666666666666</v>
       </c>
-      <c r="P33">
+      <c r="P35">
         <v>2.3174059571793588</v>
       </c>
     </row>
-    <row r="34" spans="5:16" x14ac:dyDescent="0.3">
-      <c r="E34" t="s">
+    <row r="36" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
         <v>70</v>
       </c>
-      <c r="G34">
+      <c r="G36">
         <v>25.25</v>
       </c>
-      <c r="H34">
+      <c r="H36">
         <v>0.35355339059327379</v>
       </c>
-      <c r="I34">
+      <c r="I36">
         <v>13.5</v>
       </c>
-      <c r="J34">
+      <c r="J36">
         <v>0</v>
       </c>
-      <c r="K34">
+      <c r="K36">
         <v>33.75</v>
       </c>
-      <c r="L34">
+      <c r="L36">
         <v>1.0606601717798212</v>
       </c>
-      <c r="M34">
+      <c r="M36">
         <v>24.166666666666664</v>
       </c>
-      <c r="N34">
+      <c r="N36">
         <v>0.47140452079103251</v>
       </c>
-      <c r="O34">
+      <c r="O36">
         <v>10.666666666666666</v>
       </c>
-      <c r="P34">
+      <c r="P36">
         <v>0.47140452079103251</v>
       </c>
     </row>
@@ -1375,6 +1414,554 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
+  <dimension ref="A2:AF10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" t="s">
+        <v>52</v>
+      </c>
+      <c r="V2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>19</v>
+      </c>
+      <c r="E4">
+        <v>81</v>
+      </c>
+      <c r="G4">
+        <v>86</v>
+      </c>
+      <c r="H4">
+        <v>14</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>91</v>
+      </c>
+      <c r="L4">
+        <v>69</v>
+      </c>
+      <c r="M4">
+        <v>31</v>
+      </c>
+      <c r="N4">
+        <v>40</v>
+      </c>
+      <c r="O4">
+        <v>60</v>
+      </c>
+      <c r="Q4">
+        <f>AVERAGE(C4,D4)</f>
+        <v>19.5</v>
+      </c>
+      <c r="R4">
+        <f>AVERAGE(H4,I4)</f>
+        <v>11.5</v>
+      </c>
+      <c r="S4">
+        <f>AVERAGE(M4,N4)</f>
+        <v>35.5</v>
+      </c>
+      <c r="T4">
+        <f>AVERAGE(Q4:S4)</f>
+        <v>22.166666666666668</v>
+      </c>
+      <c r="U4">
+        <f>AVERAGE(Q4:Q10)</f>
+        <v>23.714285714285715</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.STDEV.S(Q4:Q10)</f>
+        <v>2.6276913640612221</v>
+      </c>
+      <c r="W4">
+        <f>AVERAGE(R4:R10)</f>
+        <v>12.285714285714286</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.STDEV.S(R4:R10)</f>
+        <v>2.4127636791506446</v>
+      </c>
+      <c r="Y4">
+        <f>AVERAGE(S4:S10)</f>
+        <v>37.214285714285715</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.STDEV.S(S4:S10)</f>
+        <v>3.4139071318303174</v>
+      </c>
+      <c r="AA4">
+        <f>AVERAGE(T4:T10)</f>
+        <v>24.404761904761905</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.STDEV.S(T4:T10)</f>
+        <v>2.0634768009203559</v>
+      </c>
+      <c r="AC4">
+        <f>MIN(Q4:S4)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AD4">
+        <f>T4-AC4</f>
+        <v>10.666666666666668</v>
+      </c>
+      <c r="AE4">
+        <f>AVERAGE(AD4:AD10)</f>
+        <v>12.11904761904762</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.STDEV.S(AD4:AD10)</f>
+        <v>1.8148418095390031</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>86</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>70</v>
+      </c>
+      <c r="G5">
+        <v>91</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>86</v>
+      </c>
+      <c r="L5">
+        <v>64</v>
+      </c>
+      <c r="M5">
+        <v>36</v>
+      </c>
+      <c r="N5">
+        <v>29</v>
+      </c>
+      <c r="O5">
+        <v>71</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5,D5)</f>
+        <v>22</v>
+      </c>
+      <c r="R5">
+        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5,I5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5,N5)</f>
+        <v>32.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
+        <v>22</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" ref="AC5:AC10" si="4">MIN(Q5:S5)</f>
+        <v>11.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" ref="AD5:AD10" si="5">T5-AC5</f>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>74</v>
+      </c>
+      <c r="C6">
+        <v>26</v>
+      </c>
+      <c r="D6">
+        <v>23</v>
+      </c>
+      <c r="E6">
+        <v>77</v>
+      </c>
+      <c r="G6">
+        <v>81</v>
+      </c>
+      <c r="H6">
+        <v>19</v>
+      </c>
+      <c r="I6">
+        <v>12</v>
+      </c>
+      <c r="J6">
+        <v>88</v>
+      </c>
+      <c r="L6">
+        <v>66</v>
+      </c>
+      <c r="M6">
+        <v>34</v>
+      </c>
+      <c r="N6">
+        <v>48</v>
+      </c>
+      <c r="O6">
+        <v>52</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="0"/>
+        <v>24.5</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="1"/>
+        <v>15.5</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="5"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>83</v>
+      </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>70</v>
+      </c>
+      <c r="G7">
+        <v>78</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>97</v>
+      </c>
+      <c r="L7">
+        <v>74</v>
+      </c>
+      <c r="M7">
+        <v>26</v>
+      </c>
+      <c r="N7">
+        <v>53</v>
+      </c>
+      <c r="O7">
+        <v>47</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="0"/>
+        <v>23.5</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="2"/>
+        <v>39.5</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="3"/>
+        <v>25.166666666666668</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="4"/>
+        <v>12.5</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="5"/>
+        <v>12.666666666666668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B8">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>34</v>
+      </c>
+      <c r="E8">
+        <v>66</v>
+      </c>
+      <c r="G8">
+        <v>86</v>
+      </c>
+      <c r="H8">
+        <v>14</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>94</v>
+      </c>
+      <c r="L8">
+        <v>84</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+      <c r="N8">
+        <v>51</v>
+      </c>
+      <c r="O8">
+        <v>49</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="2"/>
+        <v>33.5</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="3"/>
+        <v>22.833333333333332</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="5"/>
+        <v>12.833333333333332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B9">
+        <v>71</v>
+      </c>
+      <c r="C9">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>27</v>
+      </c>
+      <c r="E9">
+        <v>73</v>
+      </c>
+      <c r="G9">
+        <v>89</v>
+      </c>
+      <c r="H9">
+        <v>11</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9">
+        <v>92</v>
+      </c>
+      <c r="L9">
+        <v>61</v>
+      </c>
+      <c r="M9">
+        <v>39</v>
+      </c>
+      <c r="N9">
+        <v>37</v>
+      </c>
+      <c r="O9">
+        <v>63</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="3"/>
+        <v>25.166666666666668</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="5"/>
+        <v>15.666666666666668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B10">
+        <v>84</v>
+      </c>
+      <c r="C10">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>31</v>
+      </c>
+      <c r="E10">
+        <v>69</v>
+      </c>
+      <c r="G10">
+        <v>78</v>
+      </c>
+      <c r="H10">
+        <v>22</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10">
+        <v>91</v>
+      </c>
+      <c r="L10">
+        <v>70</v>
+      </c>
+      <c r="M10">
+        <v>30</v>
+      </c>
+      <c r="N10">
+        <v>51</v>
+      </c>
+      <c r="O10">
+        <v>49</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="0"/>
+        <v>23.5</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="1"/>
+        <v>15.5</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="2"/>
+        <v>40.5</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="3"/>
+        <v>26.5</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="4"/>
+        <v>15.5</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25FCA91D-5E11-4BE7-9F8B-616A902FA88F}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1860,7 +2447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CA6F53-9387-444E-890F-DCD3D83EC80C}">
   <dimension ref="A1:AN99"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4563,7 +5150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C39A647-64D8-47BC-AD52-3FB80D45AD9F}">
   <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5295,7 +5882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F319F6D0-ABAC-48C6-A867-062B0035D0C5}">
   <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6012,7 +6599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76F82D8A-1A23-4CF3-9872-DA5B576CDAF9}">
   <dimension ref="A1:AR36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7243,7 +7830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8214124B-224B-4F9B-B528-181D112DB9C5}">
   <dimension ref="A1:AR36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8443,7 +9030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D9506E-E2C3-4105-A101-2ED902EAE848}">
   <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10500,7 +11087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80BAE23-A740-4698-B840-F018E78CD098}">
   <dimension ref="A1:AE5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10802,6 +11389,354 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922D1C46-6714-46BD-8134-0C2B2014CB79}">
+  <dimension ref="B1:AF5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" t="s">
+        <v>15</v>
+      </c>
+      <c r="T1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" t="s">
+        <v>52</v>
+      </c>
+      <c r="V1" t="s">
+        <v>45</v>
+      </c>
+      <c r="W1" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>81</v>
+      </c>
+      <c r="C2">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>28</v>
+      </c>
+      <c r="E2">
+        <v>72</v>
+      </c>
+      <c r="G2">
+        <v>83</v>
+      </c>
+      <c r="H2">
+        <v>17</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>90</v>
+      </c>
+      <c r="L2">
+        <v>75</v>
+      </c>
+      <c r="M2">
+        <v>25</v>
+      </c>
+      <c r="N2">
+        <v>44</v>
+      </c>
+      <c r="O2">
+        <v>56</v>
+      </c>
+      <c r="Q2">
+        <f>AVERAGE(C2:D2)</f>
+        <v>23.5</v>
+      </c>
+      <c r="R2">
+        <f>AVERAGE(H2:I2)</f>
+        <v>13.5</v>
+      </c>
+      <c r="S2">
+        <f>AVERAGE(M2:N2)</f>
+        <v>34.5</v>
+      </c>
+      <c r="T2">
+        <f>AVERAGE(Q2:S2)</f>
+        <v>23.833333333333332</v>
+      </c>
+      <c r="U2">
+        <f>AVERAGE(Q2:Q5)</f>
+        <v>23</v>
+      </c>
+      <c r="V2">
+        <f>_xlfn.STDEV.S(Q2:Q5)</f>
+        <v>1.8708286933869707</v>
+      </c>
+      <c r="W2">
+        <f>AVERAGE(R2:R5)</f>
+        <v>13.5</v>
+      </c>
+      <c r="X2">
+        <f>_xlfn.STDEV.S(R2:R5)</f>
+        <v>2.4494897427831779</v>
+      </c>
+      <c r="Y2">
+        <f>AVERAGE(S2:S5)</f>
+        <v>35.625</v>
+      </c>
+      <c r="Z2">
+        <f>_xlfn.STDEV.S(S2:S5)</f>
+        <v>0.8539125638299665</v>
+      </c>
+      <c r="AA2">
+        <f>AVERAGE(T2:T5)</f>
+        <v>24.041666666666668</v>
+      </c>
+      <c r="AB2">
+        <f>_xlfn.STDEV.S(T2:T5)</f>
+        <v>1.1656741810198499</v>
+      </c>
+      <c r="AC2">
+        <f>MIN(Q2:S2)</f>
+        <v>13.5</v>
+      </c>
+      <c r="AD2">
+        <f>T2-AC2</f>
+        <v>10.333333333333332</v>
+      </c>
+      <c r="AE2">
+        <f>AVERAGE(AD2:AD5)</f>
+        <v>10.541666666666668</v>
+      </c>
+      <c r="AF2">
+        <f>_xlfn.STDEV.S(AD2:AD5)</f>
+        <v>1.4231876063832671</v>
+      </c>
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B3">
+        <v>93</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>66</v>
+      </c>
+      <c r="G3">
+        <v>87</v>
+      </c>
+      <c r="H3">
+        <v>13</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
+        <v>92</v>
+      </c>
+      <c r="L3">
+        <v>80</v>
+      </c>
+      <c r="M3">
+        <v>20</v>
+      </c>
+      <c r="N3">
+        <v>53</v>
+      </c>
+      <c r="O3">
+        <v>47</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q5" si="0">AVERAGE(C3:D3)</f>
+        <v>20.5</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R5" si="1">AVERAGE(H3:I3)</f>
+        <v>10.5</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S5" si="2">AVERAGE(M3:N3)</f>
+        <v>36.5</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T5" si="3">AVERAGE(Q3:S3)</f>
+        <v>22.5</v>
+      </c>
+      <c r="AC3">
+        <f t="shared" ref="AC3:AC5" si="4">MIN(Q3:S3)</f>
+        <v>10.5</v>
+      </c>
+      <c r="AD3">
+        <f t="shared" ref="AD3:AD5" si="5">T3-AC3</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>81</v>
+      </c>
+      <c r="C4">
+        <v>19</v>
+      </c>
+      <c r="D4">
+        <v>31</v>
+      </c>
+      <c r="E4">
+        <v>69</v>
+      </c>
+      <c r="G4">
+        <v>86</v>
+      </c>
+      <c r="H4">
+        <v>14</v>
+      </c>
+      <c r="I4">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>87</v>
+      </c>
+      <c r="L4">
+        <v>64</v>
+      </c>
+      <c r="M4">
+        <v>36</v>
+      </c>
+      <c r="N4">
+        <v>35</v>
+      </c>
+      <c r="O4">
+        <v>65</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="1"/>
+        <v>13.5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="2"/>
+        <v>35.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="3"/>
+        <v>24.666666666666668</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" si="4"/>
+        <v>13.5</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" si="5"/>
+        <v>11.166666666666668</v>
+      </c>
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>80</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>74</v>
+      </c>
+      <c r="G5">
+        <v>79</v>
+      </c>
+      <c r="H5">
+        <v>21</v>
+      </c>
+      <c r="I5">
+        <v>12</v>
+      </c>
+      <c r="J5">
+        <v>88</v>
+      </c>
+      <c r="L5">
+        <v>76</v>
+      </c>
+      <c r="M5">
+        <v>24</v>
+      </c>
+      <c r="N5">
+        <v>48</v>
+      </c>
+      <c r="O5">
+        <v>52</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>16.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>25.166666666666668</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="4"/>
+        <v>16.5</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="5"/>
+        <v>8.6666666666666679</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D0CE18A-8B26-4E93-B497-B59E55EFEC0E}">
   <dimension ref="A2:AF13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11204,19 +12139,19 @@
         <v>53</v>
       </c>
       <c r="Q10">
-        <f t="shared" ref="Q8:Q13" si="6">AVERAGE(C10:D10)</f>
+        <f t="shared" ref="Q10:Q13" si="6">AVERAGE(C10:D10)</f>
         <v>25</v>
       </c>
       <c r="R10">
-        <f t="shared" ref="R8:R13" si="7">AVERAGE(H10:I10)</f>
+        <f t="shared" ref="R10:R13" si="7">AVERAGE(H10:I10)</f>
         <v>12</v>
       </c>
       <c r="S10">
-        <f t="shared" ref="S8:S13" si="8">AVERAGE(M10:N10)</f>
+        <f t="shared" ref="S10:S13" si="8">AVERAGE(M10:N10)</f>
         <v>30.5</v>
       </c>
       <c r="T10">
-        <f t="shared" ref="T8:T13" si="9">AVERAGE(Q10:S10)</f>
+        <f t="shared" ref="T10:T13" si="9">AVERAGE(Q10:S10)</f>
         <v>22.5</v>
       </c>
       <c r="U10">
@@ -11252,11 +12187,11 @@
         <v>1.158702978589679</v>
       </c>
       <c r="AC10">
-        <f t="shared" ref="AC8:AC13" si="10">MIN(Q10:S10)</f>
+        <f t="shared" ref="AC10:AC13" si="10">MIN(Q10:S10)</f>
         <v>12</v>
       </c>
       <c r="AD10">
-        <f t="shared" ref="AD8:AD13" si="11">T10-AC10</f>
+        <f t="shared" ref="AD10:AD13" si="11">T10-AC10</f>
         <v>10.5</v>
       </c>
       <c r="AE10">
@@ -11459,7 +12394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E557A7D-364E-47EE-A0F3-0D888512E587}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11625,7 +12560,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B67D71-588A-4985-8ACA-35F7A9B1AF58}">
   <dimension ref="A2:AF11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12028,19 +12963,19 @@
         <v>72</v>
       </c>
       <c r="Q10">
-        <f t="shared" ref="Q8:Q11" si="6">AVERAGE(C10:D10)</f>
+        <f t="shared" ref="Q10:Q11" si="6">AVERAGE(C10:D10)</f>
         <v>25.5</v>
       </c>
       <c r="R10">
-        <f t="shared" ref="R8:R11" si="7">AVERAGE(H10:I10)</f>
+        <f t="shared" ref="R10:R11" si="7">AVERAGE(H10:I10)</f>
         <v>13.5</v>
       </c>
       <c r="S10">
-        <f t="shared" ref="S8:S11" si="8">AVERAGE(M10:N10)</f>
+        <f t="shared" ref="S10:S11" si="8">AVERAGE(M10:N10)</f>
         <v>34.5</v>
       </c>
       <c r="T10">
-        <f t="shared" ref="T8:T11" si="9">AVERAGE(Q10:S10)</f>
+        <f t="shared" ref="T10:T11" si="9">AVERAGE(Q10:S10)</f>
         <v>24.5</v>
       </c>
       <c r="U10">
@@ -12076,11 +13011,11 @@
         <v>0.47140452079103251</v>
       </c>
       <c r="AC10">
-        <f t="shared" ref="AC8:AC11" si="10">MIN(Q10:S10)</f>
+        <f t="shared" ref="AC10:AC11" si="10">MIN(Q10:S10)</f>
         <v>13.5</v>
       </c>
       <c r="AD10">
-        <f t="shared" ref="AD8:AD11" si="11">T10-AC10</f>
+        <f t="shared" ref="AD10:AD11" si="11">T10-AC10</f>
         <v>11</v>
       </c>
       <c r="AE10">
@@ -12159,7 +13094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A4C68C5-0EAB-4233-98F5-D346BC512EB4}">
   <dimension ref="A2:AF38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13480,7 +14415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A366D673-4552-407C-AD95-3B60150A1024}">
   <dimension ref="A2:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13942,19 +14877,19 @@
         <v>65</v>
       </c>
       <c r="Q11">
-        <f t="shared" ref="Q9:Q12" si="6">AVERAGE(C11:D11)</f>
+        <f t="shared" ref="Q11:Q12" si="6">AVERAGE(C11:D11)</f>
         <v>21.5</v>
       </c>
       <c r="R11">
-        <f t="shared" ref="R9:R12" si="7">AVERAGE(H11:I11)</f>
+        <f t="shared" ref="R11:R12" si="7">AVERAGE(H11:I11)</f>
         <v>12.5</v>
       </c>
       <c r="S11">
-        <f t="shared" ref="S9:S12" si="8">AVERAGE(M11:N11)</f>
+        <f t="shared" ref="S11:S12" si="8">AVERAGE(M11:N11)</f>
         <v>30.5</v>
       </c>
       <c r="T11">
-        <f t="shared" ref="T9:T12" si="9">AVERAGE(Q11:S11)</f>
+        <f t="shared" ref="T11:T12" si="9">AVERAGE(Q11:S11)</f>
         <v>21.5</v>
       </c>
       <c r="U11">
@@ -13990,11 +14925,11 @@
         <v>0.8249579113843063</v>
       </c>
       <c r="AC11">
-        <f t="shared" ref="AC9:AC12" si="10">MIN(Q11:S11)</f>
+        <f t="shared" ref="AC11:AC12" si="10">MIN(Q11:S11)</f>
         <v>12.5</v>
       </c>
       <c r="AD11">
-        <f t="shared" ref="AD9:AD12" si="11">T11-AC11</f>
+        <f t="shared" ref="AD11:AD12" si="11">T11-AC11</f>
         <v>9</v>
       </c>
       <c r="AE11">
@@ -14073,7 +15008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0843B137-6F6F-47C7-80DB-2FF2B4BCD957}">
   <dimension ref="A2:AF5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14236,7 +15171,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC9CF4A-6F3D-4BA0-B506-17E3C93FB04B}">
   <dimension ref="A2:AF9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -14720,552 +15655,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8328B926-3ADF-46D7-8F68-CEFFC1D24F6E}">
-  <dimension ref="A2:AF10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" t="s">
-        <v>15</v>
-      </c>
-      <c r="T2" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" t="s">
-        <v>52</v>
-      </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>80</v>
-      </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
-      <c r="D4">
-        <v>19</v>
-      </c>
-      <c r="E4">
-        <v>81</v>
-      </c>
-      <c r="G4">
-        <v>86</v>
-      </c>
-      <c r="H4">
-        <v>14</v>
-      </c>
-      <c r="I4">
-        <v>9</v>
-      </c>
-      <c r="J4">
-        <v>91</v>
-      </c>
-      <c r="L4">
-        <v>69</v>
-      </c>
-      <c r="M4">
-        <v>31</v>
-      </c>
-      <c r="N4">
-        <v>40</v>
-      </c>
-      <c r="O4">
-        <v>60</v>
-      </c>
-      <c r="Q4">
-        <f>AVERAGE(C4,D4)</f>
-        <v>19.5</v>
-      </c>
-      <c r="R4">
-        <f>AVERAGE(H4,I4)</f>
-        <v>11.5</v>
-      </c>
-      <c r="S4">
-        <f>AVERAGE(M4,N4)</f>
-        <v>35.5</v>
-      </c>
-      <c r="T4">
-        <f>AVERAGE(Q4:S4)</f>
-        <v>22.166666666666668</v>
-      </c>
-      <c r="U4">
-        <f>AVERAGE(Q4:Q10)</f>
-        <v>23.714285714285715</v>
-      </c>
-      <c r="V4">
-        <f>_xlfn.STDEV.S(Q4:Q10)</f>
-        <v>2.6276913640612221</v>
-      </c>
-      <c r="W4">
-        <f>AVERAGE(R4:R10)</f>
-        <v>12.285714285714286</v>
-      </c>
-      <c r="X4">
-        <f>_xlfn.STDEV.S(R4:R10)</f>
-        <v>2.4127636791506446</v>
-      </c>
-      <c r="Y4">
-        <f>AVERAGE(S4:S10)</f>
-        <v>37.214285714285715</v>
-      </c>
-      <c r="Z4">
-        <f>_xlfn.STDEV.S(S4:S10)</f>
-        <v>3.4139071318303174</v>
-      </c>
-      <c r="AA4">
-        <f>AVERAGE(T4:T10)</f>
-        <v>24.404761904761905</v>
-      </c>
-      <c r="AB4">
-        <f>_xlfn.STDEV.S(T4:T10)</f>
-        <v>2.0634768009203559</v>
-      </c>
-      <c r="AC4">
-        <f>MIN(Q4:S4)</f>
-        <v>11.5</v>
-      </c>
-      <c r="AD4">
-        <f>T4-AC4</f>
-        <v>10.666666666666668</v>
-      </c>
-      <c r="AE4">
-        <f>AVERAGE(AD4:AD10)</f>
-        <v>12.11904761904762</v>
-      </c>
-      <c r="AF4">
-        <f>_xlfn.STDEV.S(AD4:AD10)</f>
-        <v>1.8148418095390031</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>86</v>
-      </c>
-      <c r="C5">
-        <v>14</v>
-      </c>
-      <c r="D5">
-        <v>30</v>
-      </c>
-      <c r="E5">
-        <v>70</v>
-      </c>
-      <c r="G5">
-        <v>91</v>
-      </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>86</v>
-      </c>
-      <c r="L5">
-        <v>64</v>
-      </c>
-      <c r="M5">
-        <v>36</v>
-      </c>
-      <c r="N5">
-        <v>29</v>
-      </c>
-      <c r="O5">
-        <v>71</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" ref="Q5:Q10" si="0">AVERAGE(C5,D5)</f>
-        <v>22</v>
-      </c>
-      <c r="R5">
-        <f t="shared" ref="R5:R10" si="1">AVERAGE(H5,I5)</f>
-        <v>11.5</v>
-      </c>
-      <c r="S5">
-        <f t="shared" ref="S5:S10" si="2">AVERAGE(M5,N5)</f>
-        <v>32.5</v>
-      </c>
-      <c r="T5">
-        <f t="shared" ref="T5:T10" si="3">AVERAGE(Q5:S5)</f>
-        <v>22</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" ref="AC5:AC10" si="4">MIN(Q5:S5)</f>
-        <v>11.5</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" ref="AD5:AD10" si="5">T5-AC5</f>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>74</v>
-      </c>
-      <c r="C6">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>23</v>
-      </c>
-      <c r="E6">
-        <v>77</v>
-      </c>
-      <c r="G6">
-        <v>81</v>
-      </c>
-      <c r="H6">
-        <v>19</v>
-      </c>
-      <c r="I6">
-        <v>12</v>
-      </c>
-      <c r="J6">
-        <v>88</v>
-      </c>
-      <c r="L6">
-        <v>66</v>
-      </c>
-      <c r="M6">
-        <v>34</v>
-      </c>
-      <c r="N6">
-        <v>48</v>
-      </c>
-      <c r="O6">
-        <v>52</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>24.5</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>15.5</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="4"/>
-        <v>15.5</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="5"/>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>83</v>
-      </c>
-      <c r="C7">
-        <v>17</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
-      <c r="E7">
-        <v>70</v>
-      </c>
-      <c r="G7">
-        <v>78</v>
-      </c>
-      <c r="H7">
-        <v>22</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>97</v>
-      </c>
-      <c r="L7">
-        <v>74</v>
-      </c>
-      <c r="M7">
-        <v>26</v>
-      </c>
-      <c r="N7">
-        <v>53</v>
-      </c>
-      <c r="O7">
-        <v>47</v>
-      </c>
-      <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>23.5</v>
-      </c>
-      <c r="R7">
-        <f t="shared" si="1"/>
-        <v>12.5</v>
-      </c>
-      <c r="S7">
-        <f t="shared" si="2"/>
-        <v>39.5</v>
-      </c>
-      <c r="T7">
-        <f t="shared" si="3"/>
-        <v>25.166666666666668</v>
-      </c>
-      <c r="AC7">
-        <f t="shared" si="4"/>
-        <v>12.5</v>
-      </c>
-      <c r="AD7">
-        <f t="shared" si="5"/>
-        <v>12.666666666666668</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>84</v>
-      </c>
-      <c r="C8">
-        <v>16</v>
-      </c>
-      <c r="D8">
-        <v>34</v>
-      </c>
-      <c r="E8">
-        <v>66</v>
-      </c>
-      <c r="G8">
-        <v>86</v>
-      </c>
-      <c r="H8">
-        <v>14</v>
-      </c>
-      <c r="I8">
-        <v>6</v>
-      </c>
-      <c r="J8">
-        <v>94</v>
-      </c>
-      <c r="L8">
-        <v>84</v>
-      </c>
-      <c r="M8">
-        <v>16</v>
-      </c>
-      <c r="N8">
-        <v>51</v>
-      </c>
-      <c r="O8">
-        <v>49</v>
-      </c>
-      <c r="Q8">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="S8">
-        <f t="shared" si="2"/>
-        <v>33.5</v>
-      </c>
-      <c r="T8">
-        <f t="shared" si="3"/>
-        <v>22.833333333333332</v>
-      </c>
-      <c r="AC8">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="AD8">
-        <f t="shared" si="5"/>
-        <v>12.833333333333332</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>71</v>
-      </c>
-      <c r="C9">
-        <v>29</v>
-      </c>
-      <c r="D9">
-        <v>27</v>
-      </c>
-      <c r="E9">
-        <v>73</v>
-      </c>
-      <c r="G9">
-        <v>89</v>
-      </c>
-      <c r="H9">
-        <v>11</v>
-      </c>
-      <c r="I9">
-        <v>8</v>
-      </c>
-      <c r="J9">
-        <v>92</v>
-      </c>
-      <c r="L9">
-        <v>61</v>
-      </c>
-      <c r="M9">
-        <v>39</v>
-      </c>
-      <c r="N9">
-        <v>37</v>
-      </c>
-      <c r="O9">
-        <v>63</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>9.5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>38</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>25.166666666666668</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="4"/>
-        <v>9.5</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="5"/>
-        <v>15.666666666666668</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>84</v>
-      </c>
-      <c r="C10">
-        <v>16</v>
-      </c>
-      <c r="D10">
-        <v>31</v>
-      </c>
-      <c r="E10">
-        <v>69</v>
-      </c>
-      <c r="G10">
-        <v>78</v>
-      </c>
-      <c r="H10">
-        <v>22</v>
-      </c>
-      <c r="I10">
-        <v>9</v>
-      </c>
-      <c r="J10">
-        <v>91</v>
-      </c>
-      <c r="L10">
-        <v>70</v>
-      </c>
-      <c r="M10">
-        <v>30</v>
-      </c>
-      <c r="N10">
-        <v>51</v>
-      </c>
-      <c r="O10">
-        <v>49</v>
-      </c>
-      <c r="Q10">
-        <f t="shared" si="0"/>
-        <v>23.5</v>
-      </c>
-      <c r="R10">
-        <f t="shared" si="1"/>
-        <v>15.5</v>
-      </c>
-      <c r="S10">
-        <f t="shared" si="2"/>
-        <v>40.5</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="3"/>
-        <v>26.5</v>
-      </c>
-      <c r="AC10">
-        <f t="shared" si="4"/>
-        <v>15.5</v>
-      </c>
-      <c r="AD10">
-        <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>